--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126077023</v>
+        <v>126077016</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727296</v>
+        <v>727121</v>
       </c>
       <c r="R5" t="n">
-        <v>7086911</v>
+        <v>7087133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,6 +1046,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1064,10 +1065,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126077016</v>
+        <v>126077023</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>91250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1076,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1100,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727121</v>
+        <v>727296</v>
       </c>
       <c r="R6" t="n">
-        <v>7087133</v>
+        <v>7086911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,7 +1144,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1766,49 +1766,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126077019</v>
+        <v>126077006</v>
       </c>
       <c r="B13" t="n">
-        <v>98338</v>
+        <v>91246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727317</v>
+        <v>727275</v>
       </c>
       <c r="R13" t="n">
-        <v>7086875</v>
+        <v>7086994</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,45 +1864,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126077006</v>
+        <v>126077019</v>
       </c>
       <c r="B14" t="n">
-        <v>91246</v>
+        <v>98338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727275</v>
+        <v>727317</v>
       </c>
       <c r="R14" t="n">
-        <v>7086994</v>
+        <v>7086875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126077011</v>
+        <v>126077008</v>
       </c>
       <c r="B16" t="n">
         <v>57648</v>
@@ -2100,20 +2100,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>727257</v>
+        <v>727283</v>
       </c>
       <c r="R16" t="n">
-        <v>7086939</v>
+        <v>7086995</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,7 +2168,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126077008</v>
+        <v>126077011</v>
       </c>
       <c r="B17" t="n">
         <v>57648</v>
@@ -2201,16 +2197,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727283</v>
+        <v>727257</v>
       </c>
       <c r="R17" t="n">
-        <v>7086995</v>
+        <v>7086939</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126077016</v>
+        <v>126077023</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>91250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727121</v>
+        <v>727296</v>
       </c>
       <c r="R5" t="n">
-        <v>7087133</v>
+        <v>7086911</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1046,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1065,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126077023</v>
+        <v>126077016</v>
       </c>
       <c r="B6" t="n">
-        <v>91250</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1076,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1100,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727296</v>
+        <v>727121</v>
       </c>
       <c r="R6" t="n">
-        <v>7086911</v>
+        <v>7087133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1143,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>126077018</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>126077020</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>126077019</v>
       </c>
       <c r="B14" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126077008</v>
+        <v>126077011</v>
       </c>
       <c r="B16" t="n">
         <v>57648</v>
@@ -2100,16 +2100,20 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>727283</v>
+        <v>727257</v>
       </c>
       <c r="R16" t="n">
-        <v>7086995</v>
+        <v>7086939</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2172,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126077011</v>
+        <v>126077008</v>
       </c>
       <c r="B17" t="n">
         <v>57648</v>
@@ -2197,20 +2201,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727257</v>
+        <v>727283</v>
       </c>
       <c r="R17" t="n">
-        <v>7086939</v>
+        <v>7086995</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126077004</v>
+        <v>126077009</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,16 +1575,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1593,24 +1593,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>revir, ej häckning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>727352</v>
+        <v>727303</v>
       </c>
       <c r="R11" t="n">
-        <v>7086828</v>
+        <v>7086908</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126077009</v>
+        <v>126077004</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,16 +1672,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1698,16 +1690,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>727303</v>
+        <v>727352</v>
       </c>
       <c r="R12" t="n">
-        <v>7086908</v>
+        <v>7086828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126077014</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>126077000</v>
       </c>
       <c r="B3" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>126077001</v>
       </c>
       <c r="B4" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>126077023</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>126077016</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>126077018</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>126077003</v>
       </c>
       <c r="B8" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>126077026</v>
       </c>
       <c r="B9" t="n">
-        <v>57572</v>
+        <v>57573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>126077020</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126077009</v>
       </c>
       <c r="B11" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>126077004</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>126077006</v>
       </c>
       <c r="B13" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>126077019</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>126077007</v>
       </c>
       <c r="B15" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>126077011</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>126077008</v>
       </c>
       <c r="B17" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>126077012</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>126077000</v>
       </c>
       <c r="B3" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>126077001</v>
       </c>
       <c r="B4" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>126077023</v>
       </c>
       <c r="B5" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>126077018</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,45 +1260,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126077003</v>
+        <v>126077026</v>
       </c>
       <c r="B8" t="n">
-        <v>91199</v>
+        <v>57573</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727234</v>
+        <v>727125</v>
       </c>
       <c r="R8" t="n">
-        <v>7087063</v>
+        <v>7087130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,53 +1365,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126077026</v>
+        <v>126077003</v>
       </c>
       <c r="B9" t="n">
-        <v>57573</v>
+        <v>91201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727125</v>
+        <v>727234</v>
       </c>
       <c r="R9" t="n">
-        <v>7087130</v>
+        <v>7087063</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,7 +1465,7 @@
         <v>126077020</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>126077006</v>
       </c>
       <c r="B13" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>126077019</v>
       </c>
       <c r="B14" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>126077000</v>
       </c>
       <c r="B3" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>126077001</v>
       </c>
       <c r="B4" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>126077023</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>126077018</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,53 +1260,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126077026</v>
+        <v>126077003</v>
       </c>
       <c r="B8" t="n">
-        <v>57573</v>
+        <v>91203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727125</v>
+        <v>727234</v>
       </c>
       <c r="R8" t="n">
-        <v>7087130</v>
+        <v>7087063</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,45 +1357,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126077003</v>
+        <v>126077026</v>
       </c>
       <c r="B9" t="n">
-        <v>91201</v>
+        <v>57573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727234</v>
+        <v>727125</v>
       </c>
       <c r="R9" t="n">
-        <v>7087063</v>
+        <v>7087130</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,7 +1465,7 @@
         <v>126077020</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>126077006</v>
       </c>
       <c r="B13" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>126077019</v>
       </c>
       <c r="B14" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -1766,45 +1766,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126077006</v>
+        <v>126077019</v>
       </c>
       <c r="B13" t="n">
-        <v>91252</v>
+        <v>98345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727275</v>
+        <v>727317</v>
       </c>
       <c r="R13" t="n">
-        <v>7086994</v>
+        <v>7086875</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,49 +1868,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126077019</v>
+        <v>126077006</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>91252</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727317</v>
+        <v>727275</v>
       </c>
       <c r="R14" t="n">
-        <v>7086875</v>
+        <v>7086994</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126077014</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>126077000</v>
       </c>
       <c r="B3" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>126077001</v>
       </c>
       <c r="B4" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>126077023</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>126077016</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>126077018</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,45 +1260,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126077003</v>
+        <v>126077026</v>
       </c>
       <c r="B8" t="n">
-        <v>91203</v>
+        <v>57577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727234</v>
+        <v>727125</v>
       </c>
       <c r="R8" t="n">
-        <v>7087063</v>
+        <v>7087130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,53 +1365,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126077026</v>
+        <v>126077003</v>
       </c>
       <c r="B9" t="n">
-        <v>57573</v>
+        <v>91207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727125</v>
+        <v>727234</v>
       </c>
       <c r="R9" t="n">
-        <v>7087130</v>
+        <v>7087063</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,7 +1465,7 @@
         <v>126077020</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126077009</v>
       </c>
       <c r="B11" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>126077004</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,49 +1766,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126077019</v>
+        <v>126077006</v>
       </c>
       <c r="B13" t="n">
-        <v>98345</v>
+        <v>91256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727317</v>
+        <v>727275</v>
       </c>
       <c r="R13" t="n">
-        <v>7086875</v>
+        <v>7086994</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,45 +1864,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126077006</v>
+        <v>126077019</v>
       </c>
       <c r="B14" t="n">
-        <v>91252</v>
+        <v>98349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727275</v>
+        <v>727317</v>
       </c>
       <c r="R14" t="n">
-        <v>7086994</v>
+        <v>7086875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
         <v>126077007</v>
       </c>
       <c r="B15" t="n">
-        <v>58131</v>
+        <v>58135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>126077011</v>
       </c>
       <c r="B16" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>126077008</v>
       </c>
       <c r="B17" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>126077012</v>
       </c>
       <c r="B18" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126077023</v>
+        <v>126077016</v>
       </c>
       <c r="B5" t="n">
-        <v>91260</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727296</v>
+        <v>727121</v>
       </c>
       <c r="R5" t="n">
-        <v>7086911</v>
+        <v>7087133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,6 +1046,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1064,10 +1065,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126077016</v>
+        <v>126077023</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1076,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1100,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727121</v>
+        <v>727296</v>
       </c>
       <c r="R6" t="n">
-        <v>7087133</v>
+        <v>7086911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,7 +1144,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126077016</v>
+        <v>126077023</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727121</v>
+        <v>727296</v>
       </c>
       <c r="R5" t="n">
-        <v>7087133</v>
+        <v>7086911</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1046,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1065,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126077023</v>
+        <v>126077016</v>
       </c>
       <c r="B6" t="n">
-        <v>91260</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1076,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1100,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727296</v>
+        <v>727121</v>
       </c>
       <c r="R6" t="n">
-        <v>7086911</v>
+        <v>7087133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1143,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>126077018</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,53 +1260,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126077026</v>
+        <v>126077003</v>
       </c>
       <c r="B8" t="n">
-        <v>57577</v>
+        <v>91207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727125</v>
+        <v>727234</v>
       </c>
       <c r="R8" t="n">
-        <v>7087130</v>
+        <v>7087063</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,45 +1357,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126077003</v>
+        <v>126077026</v>
       </c>
       <c r="B9" t="n">
-        <v>91207</v>
+        <v>57577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727234</v>
+        <v>727125</v>
       </c>
       <c r="R9" t="n">
-        <v>7087063</v>
+        <v>7087130</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,7 +1465,7 @@
         <v>126077020</v>
       </c>
       <c r="B10" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,45 +1766,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126077006</v>
+        <v>126077019</v>
       </c>
       <c r="B13" t="n">
-        <v>91256</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727275</v>
+        <v>727317</v>
       </c>
       <c r="R13" t="n">
-        <v>7086994</v>
+        <v>7086875</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,49 +1868,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126077019</v>
+        <v>126077006</v>
       </c>
       <c r="B14" t="n">
-        <v>98349</v>
+        <v>91256</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727317</v>
+        <v>727275</v>
       </c>
       <c r="R14" t="n">
-        <v>7086875</v>
+        <v>7086994</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -1766,49 +1766,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126077019</v>
+        <v>126077006</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>91256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727317</v>
+        <v>727275</v>
       </c>
       <c r="R13" t="n">
-        <v>7086875</v>
+        <v>7086994</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,45 +1864,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126077006</v>
+        <v>126077019</v>
       </c>
       <c r="B14" t="n">
-        <v>91256</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727275</v>
+        <v>727317</v>
       </c>
       <c r="R14" t="n">
-        <v>7086994</v>
+        <v>7086875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126077014</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>126077000</v>
       </c>
       <c r="B3" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>126077001</v>
       </c>
       <c r="B4" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>126077023</v>
       </c>
       <c r="B5" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>126077016</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>126077018</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>126077003</v>
       </c>
       <c r="B8" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>126077026</v>
       </c>
       <c r="B9" t="n">
-        <v>57577</v>
+        <v>57578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>126077020</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126077009</v>
       </c>
       <c r="B11" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>126077004</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>126077006</v>
       </c>
       <c r="B13" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>126077019</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>126077007</v>
       </c>
       <c r="B15" t="n">
-        <v>58135</v>
+        <v>58138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,10 +2071,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126077011</v>
+        <v>126077008</v>
       </c>
       <c r="B16" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,20 +2100,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>727257</v>
+        <v>727283</v>
       </c>
       <c r="R16" t="n">
-        <v>7086939</v>
+        <v>7086995</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,10 +2168,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126077008</v>
+        <v>126077011</v>
       </c>
       <c r="B17" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,16 +2197,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727283</v>
+        <v>727257</v>
       </c>
       <c r="R17" t="n">
-        <v>7086995</v>
+        <v>7086939</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
         <v>126077012</v>
       </c>
       <c r="B18" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -1766,45 +1766,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126077006</v>
+        <v>126077019</v>
       </c>
       <c r="B13" t="n">
-        <v>91259</v>
+        <v>98361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727275</v>
+        <v>727317</v>
       </c>
       <c r="R13" t="n">
-        <v>7086994</v>
+        <v>7086875</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,49 +1868,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126077019</v>
+        <v>126077006</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>91259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727317</v>
+        <v>727275</v>
       </c>
       <c r="R14" t="n">
-        <v>7086875</v>
+        <v>7086994</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126077023</v>
+        <v>126077016</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>80083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>727296</v>
+        <v>727121</v>
       </c>
       <c r="R5" t="n">
-        <v>7086911</v>
+        <v>7087133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,6 +1046,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1064,10 +1065,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126077016</v>
+        <v>126077023</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>91263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1076,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1100,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>727121</v>
+        <v>727296</v>
       </c>
       <c r="R6" t="n">
-        <v>7087133</v>
+        <v>7086911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,7 +1144,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,45 +1260,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126077003</v>
+        <v>126077026</v>
       </c>
       <c r="B8" t="n">
-        <v>91210</v>
+        <v>57578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>727234</v>
+        <v>727125</v>
       </c>
       <c r="R8" t="n">
-        <v>7087063</v>
+        <v>7087130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,53 +1365,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126077026</v>
+        <v>126077003</v>
       </c>
       <c r="B9" t="n">
-        <v>57578</v>
+        <v>91210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>727125</v>
+        <v>727234</v>
       </c>
       <c r="R9" t="n">
-        <v>7087130</v>
+        <v>7087063</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1766,49 +1766,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126077019</v>
+        <v>126077006</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>91259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727317</v>
+        <v>727275</v>
       </c>
       <c r="R13" t="n">
-        <v>7086875</v>
+        <v>7086994</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,45 +1864,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126077006</v>
+        <v>126077019</v>
       </c>
       <c r="B14" t="n">
-        <v>91259</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727275</v>
+        <v>727317</v>
       </c>
       <c r="R14" t="n">
-        <v>7086994</v>
+        <v>7086875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126077008</v>
+        <v>126077011</v>
       </c>
       <c r="B16" t="n">
         <v>57654</v>
@@ -2100,16 +2100,20 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>727283</v>
+        <v>727257</v>
       </c>
       <c r="R16" t="n">
-        <v>7086995</v>
+        <v>7086939</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2172,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126077011</v>
+        <v>126077008</v>
       </c>
       <c r="B17" t="n">
         <v>57654</v>
@@ -2197,20 +2201,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>727257</v>
+        <v>727283</v>
       </c>
       <c r="R17" t="n">
-        <v>7086939</v>
+        <v>7086995</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 26671-2025 artfynd.xlsx
+++ b/artfynd/A 26671-2025 artfynd.xlsx
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126077009</v>
+        <v>126077004</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,16 +1575,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1593,16 +1593,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>727303</v>
+        <v>727352</v>
       </c>
       <c r="R11" t="n">
-        <v>7086908</v>
+        <v>7086828</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126077004</v>
+        <v>126077009</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,16 +1680,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1690,24 +1698,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>revir, ej häckning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>727352</v>
+        <v>727303</v>
       </c>
       <c r="R12" t="n">
-        <v>7086828</v>
+        <v>7086908</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,45 +1766,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126077006</v>
+        <v>126077019</v>
       </c>
       <c r="B13" t="n">
-        <v>91259</v>
+        <v>98361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>727275</v>
+        <v>727317</v>
       </c>
       <c r="R13" t="n">
-        <v>7086994</v>
+        <v>7086875</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,49 +1868,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126077019</v>
+        <v>126077006</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>91259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djurholmsberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>727317</v>
+        <v>727275</v>
       </c>
       <c r="R14" t="n">
-        <v>7086875</v>
+        <v>7086994</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
